--- a/Bibsam_tidskriftslistor/scifree_data_ios.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_ios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_0A09720F20A56AE7753F57ABDD41491B4AE82915" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68F0551F-B3C6-40E2-9E3A-6D6A9BA18A7B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD67CCE3-BA58-4979-BE4C-92DB634E4F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="266">
   <si>
     <t>Open</t>
   </si>
@@ -67,42 +67,24 @@
     <t>Biorheology</t>
   </si>
   <si>
-    <t>Bladder Cancer</t>
-  </si>
-  <si>
-    <t>Breast Disease</t>
-  </si>
-  <si>
-    <t>Cancer Biomarkers</t>
-  </si>
-  <si>
     <t>Clinical Hemorheology and Microcirculation</t>
   </si>
   <si>
     <t>Computability</t>
   </si>
   <si>
-    <t>Data Science</t>
-  </si>
-  <si>
     <t>Education for Information</t>
   </si>
   <si>
     <t>Environmental Policy and Law</t>
   </si>
   <si>
-    <t>Fundamenta Informaticae</t>
-  </si>
-  <si>
     <t>Human Antibodies</t>
   </si>
   <si>
     <t>Human Systems Management</t>
   </si>
   <si>
-    <t>In Silico Biology</t>
-  </si>
-  <si>
     <t>Information Polity</t>
   </si>
   <si>
@@ -157,9 +139,6 @@
     <t>Journal of Cellular Biotechnology</t>
   </si>
   <si>
-    <t>Journal of Computational Methods in Science and Engineering</t>
-  </si>
-  <si>
     <t>Journal of Computer Security</t>
   </si>
   <si>
@@ -181,21 +160,9 @@
     <t>Journal of Neonatal-Perinatal Medicine</t>
   </si>
   <si>
-    <t>Journal of Neuromuscular Diseases</t>
-  </si>
-  <si>
     <t>Journal of Neutron Research</t>
   </si>
   <si>
-    <t>Journal of Parkinson's Disease</t>
-  </si>
-  <si>
-    <t>Journal of Pediatric Rehabilitation Medicine</t>
-  </si>
-  <si>
-    <t>Journal of Sports Analytics</t>
-  </si>
-  <si>
     <t>Journal of Vestibular Research</t>
   </si>
   <si>
@@ -205,9 +172,6 @@
     <t>Journal of X-Ray Science and Technology</t>
   </si>
   <si>
-    <t>Kidney Cancer</t>
-  </si>
-  <si>
     <t>Main Group Chemistry</t>
   </si>
   <si>
@@ -223,9 +187,6 @@
     <t>NeuroRehabilitation</t>
   </si>
   <si>
-    <t>Nutrition and Healty Aging</t>
-  </si>
-  <si>
     <t>Physiotherapy Practice and Research</t>
   </si>
   <si>
@@ -235,15 +196,9 @@
     <t>Risk and Decision Analysis</t>
   </si>
   <si>
-    <t>Semantic Web</t>
-  </si>
-  <si>
     <t>Statistical Journal of the IAOS: Journal of the International Association for Official Statistics</t>
   </si>
   <si>
-    <t>Stem Journal</t>
-  </si>
-  <si>
     <t>Strength, Fracture and Complexity</t>
   </si>
   <si>
@@ -277,36 +232,21 @@
     <t>0006-355X</t>
   </si>
   <si>
-    <t>2352-3727</t>
-  </si>
-  <si>
-    <t>0888-6008</t>
-  </si>
-  <si>
     <t>1573-2487</t>
   </si>
   <si>
-    <t>1574-0153</t>
-  </si>
-  <si>
     <t>1386-0291</t>
   </si>
   <si>
     <t>2211-3568</t>
   </si>
   <si>
-    <t>2451-8484</t>
-  </si>
-  <si>
     <t>0167-8329</t>
   </si>
   <si>
     <t>0378-777X</t>
   </si>
   <si>
-    <t>0169-2968</t>
-  </si>
-  <si>
     <t>1093-2607</t>
   </si>
   <si>
@@ -316,9 +256,6 @@
     <t>1389-6911</t>
   </si>
   <si>
-    <t>1386-6338</t>
-  </si>
-  <si>
     <t>1570-1255</t>
   </si>
   <si>
@@ -400,21 +337,9 @@
     <t>1934-5798</t>
   </si>
   <si>
-    <t>2214-3599</t>
-  </si>
-  <si>
     <t>1023-8166</t>
   </si>
   <si>
-    <t>1877-7171</t>
-  </si>
-  <si>
-    <t>1874-5393</t>
-  </si>
-  <si>
-    <t>2215-020X</t>
-  </si>
-  <si>
     <t>0957-4271</t>
   </si>
   <si>
@@ -424,9 +349,6 @@
     <t>0895-3996</t>
   </si>
   <si>
-    <t>2468-4562</t>
-  </si>
-  <si>
     <t>1024-1221</t>
   </si>
   <si>
@@ -442,9 +364,6 @@
     <t>1053-8135</t>
   </si>
   <si>
-    <t>2451-9480</t>
-  </si>
-  <si>
     <t>2213-0683</t>
   </si>
   <si>
@@ -454,15 +373,9 @@
     <t>1569-7371</t>
   </si>
   <si>
-    <t>1570-0844</t>
-  </si>
-  <si>
     <t>1874-7655</t>
   </si>
   <si>
-    <t>2468-8290</t>
-  </si>
-  <si>
     <t>1567-2069</t>
   </si>
   <si>
@@ -496,36 +409,21 @@
     <t>1878-5034</t>
   </si>
   <si>
-    <t>2352-3735</t>
-  </si>
-  <si>
-    <t>1558-1551</t>
-  </si>
-  <si>
     <t>1744-8999</t>
   </si>
   <si>
-    <t>1875-8592</t>
-  </si>
-  <si>
     <t>1875-8622</t>
   </si>
   <si>
     <t>2211-3576</t>
   </si>
   <si>
-    <t>2451-8492</t>
-  </si>
-  <si>
     <t>1875-8649</t>
   </si>
   <si>
     <t>1878-5395</t>
   </si>
   <si>
-    <t>1875-8681</t>
-  </si>
-  <si>
     <t>1875-869X</t>
   </si>
   <si>
@@ -535,9 +433,6 @@
     <t>2468-2438</t>
   </si>
   <si>
-    <t>1434-3207</t>
-  </si>
-  <si>
     <t>1875-8754</t>
   </si>
   <si>
@@ -622,18 +517,9 @@
     <t>1878-4429</t>
   </si>
   <si>
-    <t>2214-3602</t>
-  </si>
-  <si>
     <t>1477-2655</t>
   </si>
   <si>
-    <t>1877-718X</t>
-  </si>
-  <si>
-    <t>1875-8894</t>
-  </si>
-  <si>
     <t>1878-6464</t>
   </si>
   <si>
@@ -643,9 +529,6 @@
     <t>1095-9114</t>
   </si>
   <si>
-    <t xml:space="preserve">2468-4570 </t>
-  </si>
-  <si>
     <t>1745-1167</t>
   </si>
   <si>
@@ -661,9 +544,6 @@
     <t>1878-6448</t>
   </si>
   <si>
-    <t>2451-9502</t>
-  </si>
-  <si>
     <t>2213-0691</t>
   </si>
   <si>
@@ -673,15 +553,9 @@
     <t>1875-9173</t>
   </si>
   <si>
-    <t>2210-4968</t>
-  </si>
-  <si>
     <t>1875-9254</t>
   </si>
   <si>
-    <t>2468-8304</t>
-  </si>
-  <si>
     <t>1875-9262</t>
   </si>
   <si>
@@ -700,21 +574,9 @@
     <t>Hybrid</t>
   </si>
   <si>
-    <t>2215-0218</t>
-  </si>
-  <si>
-    <t>Journal of Future Robot Life</t>
-  </si>
-  <si>
-    <t>2589-9953</t>
-  </si>
-  <si>
     <t xml:space="preserve">2214-6490 </t>
   </si>
   <si>
-    <t>2589-9961</t>
-  </si>
-  <si>
     <t>2214-6512</t>
   </si>
   <si>
@@ -739,39 +601,24 @@
     <t>https://journals.sagepub.com/home/BRH</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/BLC</t>
-  </si>
-  <si>
-    <t>https://journals.sagepub.com/home/BRD</t>
-  </si>
-  <si>
     <t>Bridge Structures</t>
   </si>
   <si>
     <t>https://journals.sagepub.com/home/BRS</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/CBM</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/CHM</t>
   </si>
   <si>
     <t>https://journals.sagepub.com/home/COE</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/dsca</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/EFI</t>
   </si>
   <si>
     <t>https://journals.sagepub.com/home/EPL</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/FUN</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/HAB</t>
   </si>
   <si>
@@ -784,9 +631,6 @@
     <t>https://journals.sagepub.com/home/ICG</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/isia</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/IPO</t>
   </si>
   <si>
@@ -850,9 +694,6 @@
     <t>https://journals.sagepub.com/home/JEM</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/frl</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/HSN</t>
   </si>
   <si>
@@ -868,21 +709,9 @@
     <t>https://journals.sagepub.com/home/NPM</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/jnd</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/JNE</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/pkn</t>
-  </si>
-  <si>
-    <t>https://journals.sagepub.com/home/prm</t>
-  </si>
-  <si>
-    <t>https://journals.sagepub.com/home/san</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/VER</t>
   </si>
   <si>
@@ -892,9 +721,6 @@
     <t>https://journals.sagepub.com/home/XST</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/kca</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/MGC</t>
   </si>
   <si>
@@ -910,9 +736,6 @@
     <t>https://journals.sagepub.com/home/NRE</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/nut</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/ppr</t>
   </si>
   <si>
@@ -922,15 +745,9 @@
     <t>https://journals.sagepub.com/home/RDA</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/swj</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/SJI</t>
   </si>
   <si>
-    <t>https://journals.sagepub.com/home/ste</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/home/SFC</t>
   </si>
   <si>
@@ -970,15 +787,6 @@
     <t>https://journals.sagepub.com/home/CSW</t>
   </si>
   <si>
-    <t>2949-799X</t>
-  </si>
-  <si>
-    <t>FAIR Connect</t>
-  </si>
-  <si>
-    <t>https://journals.sagepub.com/home/fco</t>
-  </si>
-  <si>
     <t>Journal of Alzheimer's Disease Reports</t>
   </si>
   <si>
@@ -997,15 +805,6 @@
     <t>https://journals.sagepub.com/home/SMC</t>
   </si>
   <si>
-    <t>2949-8732</t>
-  </si>
-  <si>
-    <t>Neurosymbolic Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>https://neurosymbolic-ai-journal.com/content/about-neurosymbolic-artificial-intelligence</t>
-  </si>
-  <si>
     <t>3050-4554</t>
   </si>
   <si>
@@ -1018,16 +817,7 @@
     <t>https://journals.sagepub.com/home/EAI</t>
   </si>
   <si>
-    <t>1010-4283</t>
-  </si>
-  <si>
-    <t>1423-0380</t>
-  </si>
-  <si>
-    <t>Tumor Biology</t>
-  </si>
-  <si>
-    <t>https://journals.sagepub.com/home/tub</t>
+    <t>Journal of Computational Methods in Sciences and Engineering</t>
   </si>
 </sst>
 </file>
@@ -1083,19 +873,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2CE3C551-3C0E-4249-A3F7-EA964F32705E}" name="Table2" displayName="Table2" ref="A1:G83" totalsRowShown="0">
-  <autoFilter ref="A1:G83" xr:uid="{2CE3C551-3C0E-4249-A3F7-EA964F32705E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G83">
-    <sortCondition ref="D1:D83"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97C4B7A3-DAA1-4A1B-9573-61087FFF7612}" name="Table1" displayName="Table1" ref="A1:G65" totalsRowShown="0">
+  <autoFilter ref="A1:G65" xr:uid="{97C4B7A3-DAA1-4A1B-9573-61087FFF7612}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9FC3577D-6064-4D2C-863C-885125108089}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{287A126F-0C8B-426B-9474-378719A7CF50}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{A81FC236-47DD-4486-A55A-C1631EE7CABE}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{D5754D4E-4071-43DA-87B9-FC02B1070765}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{0216321E-71E3-40BC-99B3-648A52823F55}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{BEEA77D8-E67E-46D1-9601-097DE43F21DE}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{DBAF1B21-0F8C-4C2C-8EEE-586A85388F33}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{22C9DB09-05F8-487F-94F9-06D1E3CBD7CB}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{C2CD4ECA-EA9A-4462-8851-DC77BD738A42}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{558A1FAC-6346-4AF9-BD62-88BDE21283CC}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{AC6295B9-F7BF-4687-976C-06076D899657}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{7F13B995-3993-4E7A-8F39-26F581E2C0BC}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{999F657A-1604-4AD7-920C-2A801CEB6538}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{121707BF-6670-4F00-8E96-B396BA860BCC}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1363,8 +1150,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBBF26A-7D81-4404-B602-B17E7DF52901}">
-  <dimension ref="A1:G83"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B4AC5-1B7D-4EFF-B6D7-0354E63F45EC}">
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1404,22 +1191,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="F2" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G2" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1427,22 +1214,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>233</v>
+        <v>187</v>
       </c>
       <c r="F3" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G3" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,22 +1237,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G4" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1473,22 +1260,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1496,22 +1283,22 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G6" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1519,22 +1306,22 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="F7" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G7" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1542,22 +1329,22 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="F8" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1565,22 +1352,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="E9" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G9" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1588,22 +1375,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G10" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1611,22 +1398,22 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G11" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1634,22 +1421,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="F12" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G12" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1657,22 +1444,22 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="F13" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1680,22 +1467,22 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G14" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1703,22 +1490,22 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G15" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1726,22 +1513,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="F16" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G16" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1749,22 +1536,22 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="F17" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G17" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1772,19 +1559,22 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>316</v>
+        <v>138</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>317</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>318</v>
+        <v>204</v>
       </c>
       <c r="F18" t="s">
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1792,22 +1582,22 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="F19" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G19" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1815,22 +1605,22 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="F20" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G20" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1838,22 +1628,22 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="F21" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1861,22 +1651,22 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>252</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="F22" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G22" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1884,22 +1674,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="F23" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G23" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1907,22 +1697,22 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="F24" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G24" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1930,22 +1720,22 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="F25" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G25" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1953,22 +1743,22 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G26" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1976,22 +1766,22 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="F27" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G27" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1999,22 +1789,22 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
       <c r="E28" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="F28" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G28" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2022,22 +1812,22 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="F29" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G29" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2045,22 +1835,22 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="F30" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G30" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2068,22 +1858,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="F31" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G31" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2091,22 +1881,19 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
-      </c>
-      <c r="C32" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>255</v>
       </c>
       <c r="E32" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F32" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2114,22 +1901,22 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="F33" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2137,22 +1924,22 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E34" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="F34" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G34" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2160,22 +1947,22 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>307</v>
+        <v>219</v>
       </c>
       <c r="F35" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G35" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2183,22 +1970,22 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
         <v>38</v>
       </c>
       <c r="E36" t="s">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="F36" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G36" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2206,22 +1993,22 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>265</v>
       </c>
       <c r="E37" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="F37" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G37" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2229,22 +2016,22 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="F38" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G38" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2252,19 +2039,22 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>186</v>
+        <v>159</v>
+      </c>
+      <c r="C39" t="s">
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>320</v>
+        <v>223</v>
       </c>
       <c r="F39" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G39" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2272,22 +2062,22 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
         <v>41</v>
       </c>
       <c r="E40" t="s">
-        <v>269</v>
+        <v>224</v>
       </c>
       <c r="F40" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G40" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2295,22 +2085,22 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
         <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F41" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G41" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2318,22 +2108,22 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
         <v>43</v>
       </c>
       <c r="E42" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G42" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2341,22 +2131,22 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
         <v>44</v>
       </c>
       <c r="E43" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="F43" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G43" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2364,22 +2154,22 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
         <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="F44" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G44" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2387,22 +2177,22 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
         <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="F45" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G45" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2410,22 +2200,22 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="C46" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="E46" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="F46" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G46" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2433,22 +2223,22 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" t="s">
         <v>230</v>
       </c>
-      <c r="C47" t="s">
-        <v>228</v>
-      </c>
-      <c r="D47" t="s">
-        <v>227</v>
-      </c>
-      <c r="E47" t="s">
-        <v>276</v>
-      </c>
       <c r="F47" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G47" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2456,22 +2246,22 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D48" t="s">
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="F48" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G48" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2479,22 +2269,22 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
       </c>
       <c r="E49" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="F49" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G49" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2502,22 +2292,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
         <v>50</v>
       </c>
       <c r="E50" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="F50" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G50" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2525,22 +2315,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
         <v>51</v>
       </c>
       <c r="E51" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="F51" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G51" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,22 +2338,22 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
         <v>52</v>
       </c>
       <c r="E52" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="F52" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G52" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,22 +2361,22 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
         <v>53</v>
       </c>
       <c r="E53" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="F53" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G53" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2594,22 +2384,22 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
         <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="F54" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G54" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,22 +2407,22 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
         <v>55</v>
       </c>
       <c r="E55" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="F55" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G55" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2640,22 +2430,22 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D56" t="s">
         <v>56</v>
       </c>
       <c r="E56" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="F56" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G56" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2663,22 +2453,22 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>321</v>
+        <v>176</v>
       </c>
       <c r="C57" t="s">
-        <v>322</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>323</v>
+        <v>57</v>
       </c>
       <c r="E57" t="s">
-        <v>324</v>
+        <v>240</v>
       </c>
       <c r="F57" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G57" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2686,22 +2476,22 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E58" t="s">
-        <v>286</v>
+        <v>241</v>
       </c>
       <c r="F58" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G58" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2709,22 +2499,22 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E59" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="F59" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G59" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2732,22 +2522,22 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E60" t="s">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G60" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2755,22 +2545,22 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="C61" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E61" t="s">
-        <v>289</v>
+        <v>244</v>
       </c>
       <c r="F61" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G61" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2778,22 +2568,22 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>261</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
       <c r="E62" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="F62" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G62" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2801,22 +2591,22 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C63" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="F63" t="s">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2824,22 +2614,22 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="C64" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E64" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="F64" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G64" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2847,433 +2637,22 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E65" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="F65" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="G65" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" t="s">
-        <v>211</v>
-      </c>
-      <c r="C66" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" t="s">
-        <v>65</v>
-      </c>
-      <c r="E66" t="s">
-        <v>294</v>
-      </c>
-      <c r="F66" t="s">
-        <v>225</v>
-      </c>
-      <c r="G66" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>8</v>
-      </c>
-      <c r="B67" t="s">
-        <v>212</v>
-      </c>
-      <c r="C67" t="s">
-        <v>139</v>
-      </c>
-      <c r="D67" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" t="s">
-        <v>295</v>
-      </c>
-      <c r="F67" t="s">
-        <v>225</v>
-      </c>
-      <c r="G67" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68" t="s">
-        <v>325</v>
-      </c>
-      <c r="D68" t="s">
-        <v>326</v>
-      </c>
-      <c r="E68" t="s">
-        <v>327</v>
-      </c>
-      <c r="F68" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69" t="s">
-        <v>213</v>
-      </c>
-      <c r="C69" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" t="s">
-        <v>67</v>
-      </c>
-      <c r="E69" t="s">
-        <v>296</v>
-      </c>
-      <c r="F69" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>8</v>
-      </c>
-      <c r="B70" t="s">
-        <v>214</v>
-      </c>
-      <c r="C70" t="s">
-        <v>141</v>
-      </c>
-      <c r="D70" t="s">
-        <v>68</v>
-      </c>
-      <c r="E70" t="s">
-        <v>297</v>
-      </c>
-      <c r="F70" t="s">
-        <v>225</v>
-      </c>
-      <c r="G70" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>8</v>
-      </c>
-      <c r="B71" t="s">
-        <v>215</v>
-      </c>
-      <c r="C71" t="s">
-        <v>142</v>
-      </c>
-      <c r="D71" t="s">
-        <v>69</v>
-      </c>
-      <c r="E71" t="s">
-        <v>298</v>
-      </c>
-      <c r="F71" t="s">
-        <v>225</v>
-      </c>
-      <c r="G71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>8</v>
-      </c>
-      <c r="B72" t="s">
-        <v>216</v>
-      </c>
-      <c r="C72" t="s">
-        <v>143</v>
-      </c>
-      <c r="D72" t="s">
-        <v>70</v>
-      </c>
-      <c r="E72" t="s">
-        <v>299</v>
-      </c>
-      <c r="F72" t="s">
-        <v>225</v>
-      </c>
-      <c r="G72" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>8</v>
-      </c>
-      <c r="B73" t="s">
-        <v>217</v>
-      </c>
-      <c r="C73" t="s">
-        <v>144</v>
-      </c>
-      <c r="D73" t="s">
-        <v>71</v>
-      </c>
-      <c r="E73" t="s">
-        <v>300</v>
-      </c>
-      <c r="F73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>8</v>
-      </c>
-      <c r="B74" t="s">
-        <v>218</v>
-      </c>
-      <c r="C74" t="s">
-        <v>145</v>
-      </c>
-      <c r="D74" t="s">
-        <v>72</v>
-      </c>
-      <c r="E74" t="s">
-        <v>301</v>
-      </c>
-      <c r="F74" t="s">
-        <v>225</v>
-      </c>
-      <c r="G74" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>8</v>
-      </c>
-      <c r="B75" t="s">
-        <v>219</v>
-      </c>
-      <c r="C75" t="s">
-        <v>146</v>
-      </c>
-      <c r="D75" t="s">
-        <v>73</v>
-      </c>
-      <c r="E75" t="s">
-        <v>302</v>
-      </c>
-      <c r="F75" t="s">
-        <v>0</v>
-      </c>
-      <c r="G75" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>8</v>
-      </c>
-      <c r="B76" t="s">
-        <v>220</v>
-      </c>
-      <c r="C76" t="s">
-        <v>147</v>
-      </c>
-      <c r="D76" t="s">
-        <v>74</v>
-      </c>
-      <c r="E76" t="s">
-        <v>303</v>
-      </c>
-      <c r="F76" t="s">
-        <v>225</v>
-      </c>
-      <c r="G76" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>8</v>
-      </c>
-      <c r="B77" t="s">
-        <v>221</v>
-      </c>
-      <c r="C77" t="s">
-        <v>148</v>
-      </c>
-      <c r="D77" t="s">
-        <v>75</v>
-      </c>
-      <c r="E77" t="s">
-        <v>304</v>
-      </c>
-      <c r="F77" t="s">
-        <v>225</v>
-      </c>
-      <c r="G77" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>8</v>
-      </c>
-      <c r="B78" t="s">
-        <v>222</v>
-      </c>
-      <c r="C78" t="s">
-        <v>149</v>
-      </c>
-      <c r="D78" t="s">
-        <v>76</v>
-      </c>
-      <c r="E78" t="s">
-        <v>305</v>
-      </c>
-      <c r="F78" t="s">
-        <v>225</v>
-      </c>
-      <c r="G78" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>8</v>
-      </c>
-      <c r="B79" t="s">
-        <v>328</v>
-      </c>
-      <c r="C79" t="s">
-        <v>329</v>
-      </c>
-      <c r="D79" t="s">
-        <v>330</v>
-      </c>
-      <c r="E79" t="s">
-        <v>331</v>
-      </c>
-      <c r="F79" t="s">
-        <v>225</v>
-      </c>
-      <c r="G79" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>8</v>
-      </c>
-      <c r="B80" t="s">
-        <v>231</v>
-      </c>
-      <c r="C80" t="s">
-        <v>229</v>
-      </c>
-      <c r="D80" t="s">
-        <v>308</v>
-      </c>
-      <c r="E80" t="s">
-        <v>309</v>
-      </c>
-      <c r="F80" t="s">
-        <v>0</v>
-      </c>
-      <c r="G80" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>8</v>
-      </c>
-      <c r="B81" t="s">
-        <v>332</v>
-      </c>
-      <c r="C81" t="s">
-        <v>333</v>
-      </c>
-      <c r="D81" t="s">
-        <v>334</v>
-      </c>
-      <c r="E81" t="s">
-        <v>335</v>
-      </c>
-      <c r="F81" t="s">
-        <v>0</v>
-      </c>
-      <c r="G81" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82" t="s">
-        <v>223</v>
-      </c>
-      <c r="C82" t="s">
-        <v>150</v>
-      </c>
-      <c r="D82" t="s">
-        <v>77</v>
-      </c>
-      <c r="E82" t="s">
-        <v>310</v>
-      </c>
-      <c r="F82" t="s">
-        <v>225</v>
-      </c>
-      <c r="G82" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>8</v>
-      </c>
-      <c r="B83" t="s">
-        <v>224</v>
-      </c>
-      <c r="C83" t="s">
-        <v>151</v>
-      </c>
-      <c r="D83" t="s">
-        <v>78</v>
-      </c>
-      <c r="E83" t="s">
-        <v>311</v>
-      </c>
-      <c r="F83" t="s">
-        <v>225</v>
-      </c>
-      <c r="G83" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
